--- a/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T14:14:19+00:00</t>
+    <t>2024-09-11T08:50:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-11T08:50:28+00:00</t>
+    <t>2024-09-11T08:56:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TestModuleADRAM/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-11T08:56:43+00:00</t>
+    <t>2024-09-13T12:36:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
